--- a/checklist_forms/030_kitchen_inventory_checklist--checklist_forms.xlsx
+++ b/checklist_forms/030_kitchen_inventory_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kitchen_inventory_checklist_page_1</t>
+          <t>stock_levels_pantry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>stock_levels</t>
+          <t>Stock Levels</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kitchen_area_1_stock_levels</t>
+          <t>stock_levels_refrigerator</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>stock_levels</t>
+          <t>Stock Levels Refrigerator</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kitchen_area_2_stock_levels</t>
+          <t>stock_levels_freezer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stock_levels</t>
+          <t>Stock Levels Freezer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kitchen_area_3_stock_levels</t>
+          <t>stock_levels_dishware</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>stock_levels</t>
+          <t>Stock Levels Dishware</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kitchen_area_4_stock_levels</t>
+          <t>urgent_restocking_needs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>stock_levels</t>
+          <t>Urgent Restocking Needs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs</t>
+          <t>urgent_restocking_needs_pantry</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs</t>
+          <t>Urgent Restocking Needs Pantry</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_1</t>
+          <t>urgent_restocking_needs_refrigerator</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs</t>
+          <t>Urgent Restocking Needs Refrigerator</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_2</t>
+          <t>urgent_restocking_needs_freezer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs</t>
+          <t>Urgent Restocking Needs Freezer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>maintenance_issues</t>
+          <t>Maintenance Issues</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>maintenance_issues_1</t>
+          <t>maintenance_issues_pantry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>maintenance_issues</t>
+          <t>Maintenance Issues Pantry</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>maintenance_issues_2</t>
+          <t>maintenance_issues_refrigerator</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>maintenance_issues</t>
+          <t>Maintenance Issues Refrigerator</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>kitchen_area_1_comments</t>
+          <t>maintenance_issues_freezer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Maintenance Issues Freezer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments_1</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>comments_2</t>
+          <t>comments_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments_3</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,223 +865,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kitchen_area_2_comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>comments_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>kitchen_area_3_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>kitchen_area_4_comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>kitchen_area_5_comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>kitchen_area_6_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>kitchen_area_7_comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>kitchen_area_8_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>kitchen_area_9_comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>kitchen_area_10_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +919,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kitchen_inventory_checklist_page_1_choices</t>
+          <t>stock_levels_pantry_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +936,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kitchen_inventory_checklist_page_1_choices</t>
+          <t>stock_levels_pantry_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,58 +953,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kitchen_area_1_stock_levels_choices</t>
+          <t>stock_levels_refrigerator_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Low', 'label': 'Low'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kitchen_area_1_stock_levels_choices</t>
+          <t>stock_levels_refrigerator_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'High', 'label': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kitchen_area_1_stock_levels_choices</t>
+          <t>stock_levels_refrigerator_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kitchen_area_2_stock_levels_choices</t>
+          <t>stock_levels_freezer_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kitchen_area_2_stock_levels_choices</t>
+          <t>stock_levels_freezer_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,187 +1038,187 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kitchen_area_3_stock_levels_choices</t>
+          <t>stock_levels_dishware_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Low', 'label': 'Low'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kitchen_area_3_stock_levels_choices</t>
+          <t>stock_levels_dishware_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'High', 'label': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kitchen_area_3_stock_levels_choices</t>
+          <t>stock_levels_dishware_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kitchen_area_4_stock_levels_choices</t>
+          <t>urgent_restocking_needs_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kitchen_area_4_stock_levels_choices</t>
+          <t>urgent_restocking_needs_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_choices</t>
+          <t>urgent_restocking_needs_pantry_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_choices</t>
+          <t>urgent_restocking_needs_pantry_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_1_choices</t>
+          <t>urgent_restocking_needs_refrigerator_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_1_choices</t>
+          <t>urgent_restocking_needs_refrigerator_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_2_choices</t>
+          <t>urgent_restocking_needs_freezer_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>urgent_restocking_needs_2_choices</t>
+          <t>urgent_restocking_needs_freezer_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1454,80 +1247,114 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>maintenance_issues_1_choices</t>
+          <t>maintenance_issues_pantry_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>maintenance_issues_1_choices</t>
+          <t>maintenance_issues_pantry_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>maintenance_issues_2_choices</t>
+          <t>maintenance_issues_refrigerator_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>maintenance_issues_2_choices</t>
+          <t>maintenance_issues_refrigerator_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>maintenance_issues_freezer_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>maintenance_issues_freezer_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
